--- a/artfynd/A 42622-2022 artfynd.xlsx
+++ b/artfynd/A 42622-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130667655</v>
       </c>
       <c r="B2" t="n">
-        <v>93078</v>
+        <v>93079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42622-2022 artfynd.xlsx
+++ b/artfynd/A 42622-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130667655</v>
       </c>
       <c r="B2" t="n">
-        <v>93079</v>
+        <v>93081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42622-2022 artfynd.xlsx
+++ b/artfynd/A 42622-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130667655</v>
       </c>
       <c r="B2" t="n">
-        <v>93081</v>
+        <v>93085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42622-2022 artfynd.xlsx
+++ b/artfynd/A 42622-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130667655</v>
       </c>
       <c r="B2" t="n">
-        <v>93085</v>
+        <v>93098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42622-2022 artfynd.xlsx
+++ b/artfynd/A 42622-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130667655</v>
       </c>
       <c r="B2" t="n">
-        <v>93098</v>
+        <v>93099</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42622-2022 artfynd.xlsx
+++ b/artfynd/A 42622-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130667655</v>
       </c>
       <c r="B2" t="n">
-        <v>93099</v>
+        <v>93100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42622-2022 artfynd.xlsx
+++ b/artfynd/A 42622-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130667655</v>
       </c>
       <c r="B2" t="n">
-        <v>93100</v>
+        <v>93109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42622-2022 artfynd.xlsx
+++ b/artfynd/A 42622-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130667655</v>
       </c>
       <c r="B2" t="n">
-        <v>93133</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
